--- a/target/test-classes/testdata/LoginTestData.xlsx
+++ b/target/test-classes/testdata/LoginTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRASHANTH\eclipse-workspace\E2EAutomationFramework\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8D8BC7-44A0-474F-9A8C-2AEE4C6F1BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85962360-A290-412F-A2DD-D69A4639586C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="2480" windowWidth="19200" windowHeight="11170" xr2:uid="{594AC24F-5A86-4CC9-987B-8DD1F8C0B21A}"/>
+    <workbookView xWindow="3310" yWindow="2480" windowWidth="19200" windowHeight="11170" xr2:uid="{594AC24F-5A86-4CC9-987B-8DD1F8C0B21A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -494,7 +494,7 @@
     <col min="2" max="2" width="23.6328125" customWidth="1"/>
     <col min="3" max="3" width="19.1796875" customWidth="1"/>
     <col min="4" max="4" width="19.36328125" customWidth="1"/>
-    <col min="5" max="5" width="30.6328125" customWidth="1"/>
+    <col min="5" max="5" width="31.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">

--- a/target/test-classes/testdata/LoginTestData.xlsx
+++ b/target/test-classes/testdata/LoginTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRASHANTH\eclipse-workspace\E2EAutomationFramework\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85962360-A290-412F-A2DD-D69A4639586C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36A5E81-9209-4FAB-9C48-019CC0B73C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3310" yWindow="2480" windowWidth="19200" windowHeight="11170" xr2:uid="{594AC24F-5A86-4CC9-987B-8DD1F8C0B21A}"/>
+    <workbookView xWindow="260" yWindow="2480" windowWidth="19200" windowHeight="11170" xr2:uid="{594AC24F-5A86-4CC9-987B-8DD1F8C0B21A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
   <si>
     <t>TestCase</t>
   </si>
@@ -42,100 +42,121 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Valid Login 1</t>
-  </si>
-  <si>
     <t>standard_user</t>
   </si>
   <si>
     <t>secret_sauce</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>Standard user with valid credentials</t>
-  </si>
-  <si>
-    <t>Valid Login 2</t>
-  </si>
-  <si>
-    <t>problem_user</t>
-  </si>
-  <si>
-    <t>Problem user with valid credentials</t>
-  </si>
-  <si>
-    <t>Valid Login 3</t>
-  </si>
-  <si>
-    <t>performance_glitch_user</t>
-  </si>
-  <si>
-    <t>Performance glitch user</t>
-  </si>
-  <si>
-    <t>Valid Login 4</t>
-  </si>
-  <si>
-    <t>error_user</t>
-  </si>
-  <si>
-    <t>Error user with valid credentials</t>
-  </si>
-  <si>
-    <t>Valid Login 5</t>
-  </si>
-  <si>
-    <t>visual_user</t>
-  </si>
-  <si>
-    <t>Visual user with valid credentials</t>
-  </si>
-  <si>
-    <t>Invalid Login 1</t>
-  </si>
-  <si>
     <t>invalid_user</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
-    <t>Invalid username</t>
-  </si>
-  <si>
-    <t>Invalid Login 2</t>
-  </si>
-  <si>
     <t>wrong_password</t>
   </si>
   <si>
-    <t>Invalid password</t>
-  </si>
-  <si>
-    <t>Invalid Login 3</t>
-  </si>
-  <si>
-    <t>Empty username</t>
-  </si>
-  <si>
-    <t>Invalid Login 4</t>
-  </si>
-  <si>
-    <t>Empty password</t>
-  </si>
-  <si>
-    <t>Invalid Login 5</t>
-  </si>
-  <si>
-    <t>locked_out_user</t>
-  </si>
-  <si>
-    <t>locked</t>
-  </si>
-  <si>
-    <t>Locked out user</t>
+    <t>TestType</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>PostalCode</t>
+  </si>
+  <si>
+    <t>Login Test</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>Valid login test</t>
+  </si>
+  <si>
+    <t>addtocart</t>
+  </si>
+  <si>
+    <t>Add products to cart test</t>
+  </si>
+  <si>
+    <t>Checkout Test</t>
+  </si>
+  <si>
+    <t>checkout</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>Complete checkout test</t>
+  </si>
+  <si>
+    <t>Order Complete Test</t>
+  </si>
+  <si>
+    <t>fullorder</t>
+  </si>
+  <si>
+    <t>Full order completion test</t>
+  </si>
+  <si>
+    <t>Invalid Credentials 1</t>
+  </si>
+  <si>
+    <t>fail</t>
+  </si>
+  <si>
+    <t>Invalid Credentials 2</t>
+  </si>
+  <si>
+    <t>Invalid Website Test</t>
+  </si>
+  <si>
+    <t>invalidurl</t>
+  </si>
+  <si>
+    <t>Invalid Details Test</t>
+  </si>
+  <si>
+    <t>invaliddetails</t>
+  </si>
+  <si>
+    <t>Add to Cart Test</t>
+  </si>
+  <si>
+    <t>Valid User Test</t>
+  </si>
+  <si>
+    <t>Another valid login test</t>
+  </si>
+  <si>
+    <t>loginfail</t>
+  </si>
+  <si>
+    <t>Invalid username - MUST FAIL</t>
+  </si>
+  <si>
+    <t>Invalid password - MUST FAIL</t>
+  </si>
+  <si>
+    <t>Empty Credentials Test</t>
+  </si>
+  <si>
+    <t>Empty credentials - MUST FAIL</t>
+  </si>
+  <si>
+    <t>Invalid URL - MUST FAIL</t>
+  </si>
+  <si>
+    <t>Empty checkout details - MUST FAIL</t>
   </si>
 </sst>
 </file>
@@ -487,17 +508,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32E7022-E580-499F-BFA7-1A846A9F400E}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.90625" customWidth="1"/>
-    <col min="2" max="2" width="23.6328125" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
-    <col min="4" max="4" width="19.36328125" customWidth="1"/>
-    <col min="5" max="5" width="31.453125" customWidth="1"/>
+    <col min="1" max="1" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" customWidth="1"/>
+    <col min="9" max="9" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,171 +536,231 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>12345</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>12345</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
+      <c r="I10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
         <v>6</v>
       </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
+      <c r="I11" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
